--- a/cotacoes/2026-09-08/fechamento/PEDIDO_DIMEC_09-09-2026.xlsx
+++ b/cotacoes/2026-09-08/fechamento/PEDIDO_DIMEC_09-09-2026.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q175"/>
+  <dimension ref="A1:Q165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -632,7 +632,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr"/>
@@ -695,7 +695,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr"/>
@@ -758,7 +758,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr"/>
@@ -821,7 +821,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr"/>
@@ -884,7 +884,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr"/>
@@ -947,7 +947,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +0.2% (aceito, lim 5%)</t>
+          <t>REAJUSTE +0.2% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr"/>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +5.7% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +5.7% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr"/>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +0.2% (aceito, lim 5%)</t>
+          <t>REAJUSTE +0.2% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr"/>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr"/>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +0.2% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +0.2% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr"/>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr"/>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr"/>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +0.5% (aceito, lim 5%)</t>
+          <t>REAJUSTE +0.5% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr"/>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr"/>
@@ -2235,41 +2235,41 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>619101</v>
+        <v>538061</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>143</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>7898953484243</t>
+          <t>7898031310303</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>BICO P/ SERINGA DE LAVAGEN NASAL C/2</t>
+          <t>BICARBONATO DE SODIO 100G</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>4.3</v>
+        <v>3.23</v>
       </c>
       <c r="I28" s="5">
         <f>G28*H28</f>
@@ -2280,13 +2280,13 @@
         <v/>
       </c>
       <c r="K28" s="5" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>4.3</v>
+        <v>3.049999999999999</v>
       </c>
       <c r="N28" s="6">
         <f>J28/M28-1</f>
@@ -2298,41 +2298,41 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +5.9% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>3893</v>
+        <v>619101</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>7444</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>7908414448933</t>
+          <t>7898953484243</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>BOLSA TERMICA GEL AZUL HC353</t>
+          <t>BICO P/ SERINGA DE LAVAGEN NASAL C/2</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>12.92</v>
+        <v>4.3</v>
       </c>
       <c r="I29" s="5">
         <f>G29*H29</f>
@@ -2343,13 +2343,13 @@
         <v/>
       </c>
       <c r="K29" s="5" t="n">
-        <v>12.92</v>
+        <v>4.3</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>12.92</v>
+        <v>4.3</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>12.92</v>
+        <v>4.3</v>
       </c>
       <c r="N29" s="6">
         <f>J29/M29-1</f>
@@ -2361,41 +2361,41 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>674321</v>
+        <v>3893</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>9959</t>
+          <t>7444</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>7898975719040</t>
+          <t>7908414448933</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>BOLSA TERMICA GEL QUENTE OU FRIO GRANDE</t>
+          <t>BOLSA TERMICA GEL AZUL HC353</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>10.63</v>
+        <v>12.92</v>
       </c>
       <c r="I30" s="5">
         <f>G30*H30</f>
@@ -2406,13 +2406,13 @@
         <v/>
       </c>
       <c r="K30" s="5" t="n">
-        <v>10.63</v>
+        <v>12.92</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>10.63</v>
+        <v>12.92</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>10.63</v>
+        <v>12.92</v>
       </c>
       <c r="N30" s="6">
         <f>J30/M30-1</f>
@@ -2424,41 +2424,41 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>194</v>
+        <v>674321</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>10651</t>
+          <t>9959</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>7894164010264</t>
+          <t>7898975719040</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>BROMOPRIDA 4MG/ML 20ML</t>
+          <t>BOLSA TERMICA GEL QUENTE OU FRIO GRANDE</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>3.58</v>
+        <v>10.63</v>
       </c>
       <c r="I31" s="5">
         <f>G31*H31</f>
@@ -2469,13 +2469,13 @@
         <v/>
       </c>
       <c r="K31" s="5" t="n">
-        <v>3.58</v>
+        <v>10.63</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>3.58</v>
+        <v>10.63</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>3.58</v>
+        <v>10.63</v>
       </c>
       <c r="N31" s="6">
         <f>J31/M31-1</f>
@@ -2487,41 +2487,41 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>294981</v>
+        <v>194</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>10651</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>7896472513284</t>
+          <t>7894164010264</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>BUPROVIL 300MG CX 20 COMP</t>
+          <t>BROMOPRIDA 4MG/ML 20ML</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>5.63</v>
+        <v>3.58</v>
       </c>
       <c r="I32" s="5">
         <f>G32*H32</f>
@@ -2532,13 +2532,13 @@
         <v/>
       </c>
       <c r="K32" s="5" t="n">
-        <v>5.63</v>
+        <v>3.58</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>5.63</v>
+        <v>3.58</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>5.63</v>
+        <v>3.58</v>
       </c>
       <c r="N32" s="6">
         <f>J32/M32-1</f>
@@ -2550,41 +2550,41 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>74721</v>
+        <v>294981</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>7899620910164</t>
+          <t>7896472513284</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>CAPTOPRIL 50MG CX 30 COMP</t>
+          <t>BUPROVIL 300MG CX 20 COMP</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>4.04</v>
+        <v>5.63</v>
       </c>
       <c r="I33" s="5">
         <f>G33*H33</f>
@@ -2595,13 +2595,13 @@
         <v/>
       </c>
       <c r="K33" s="5" t="n">
-        <v>4.04</v>
+        <v>5.63</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>4.04</v>
+        <v>5.63</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>4.04</v>
+        <v>5.63</v>
       </c>
       <c r="N33" s="6">
         <f>J33/M33-1</f>
@@ -2613,41 +2613,41 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>86481</v>
+        <v>74721</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>7896004718309</t>
+          <t>7899620910164</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>CEDROXIL 500MG CX 8 CAP</t>
+          <t>CAPTOPRIL 50MG CX 30 COMP</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>9.789999999999999</v>
+        <v>4.04</v>
       </c>
       <c r="I34" s="5">
         <f>G34*H34</f>
@@ -2658,13 +2658,13 @@
         <v/>
       </c>
       <c r="K34" s="5" t="n">
-        <v>9.4</v>
+        <v>4.04</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>9.35</v>
+        <v>4.04</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>9.35</v>
+        <v>4.04</v>
       </c>
       <c r="N34" s="6">
         <f>J34/M34-1</f>
@@ -2676,28 +2676,28 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +4.1% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>630661</v>
+        <v>86481</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>7896920304556</t>
+          <t>7896004718309</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>CENTROMAX A Z 60 CAPS</t>
+          <t>CEDROXIL 500MG CX 8 CAP</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
@@ -2710,7 +2710,7 @@
         <v>1</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>28.48981</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="I35" s="5">
         <f>G35*H35</f>
@@ -2721,13 +2721,13 @@
         <v/>
       </c>
       <c r="K35" s="5" t="n">
-        <v>26.85</v>
+        <v>9.4</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>26.85</v>
+        <v>9.35</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>26.85</v>
+        <v>9.35</v>
       </c>
       <c r="N35" s="6">
         <f>J35/M35-1</f>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +6.1% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +4.7% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr"/>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.1% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +3.1% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr"/>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr"/>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.0% (aceito, lim 5%)</t>
+          <t>REAJUSTE +3.0% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr"/>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr"/>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr"/>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr"/>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr"/>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr"/>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr"/>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr"/>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +1.6% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +1.6% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr"/>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.8% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +3.8% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr"/>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr"/>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.0% (aceito, lim 5%)</t>
+          <t>REAJUSTE +3.0% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr"/>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr"/>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.5% (aceito, lim 5%)</t>
+          <t>REAJUSTE +3.5% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr"/>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr"/>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +0.1% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +0.1% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr"/>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr"/>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr"/>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.6% (aceito, lim 5%)</t>
+          <t>REAJUSTE +2.6% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr"/>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr"/>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr"/>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr"/>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr"/>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr"/>
@@ -5125,7 +5125,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr"/>
@@ -5188,41 +5188,41 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>550941</v>
+        <v>606861</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>7894488000101</t>
+          <t>7894164005239</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>FLOCONETES SEGUROS E ABSORVENTES 75UN</t>
+          <t>FLEXENEMA 130ML (ARL)</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>1.35</v>
+        <v>14.17</v>
       </c>
       <c r="I75" s="5">
         <f>G75*H75</f>
@@ -5233,13 +5233,13 @@
         <v/>
       </c>
       <c r="K75" s="5" t="n">
-        <v>1.35</v>
+        <v>13.49</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>1.35</v>
+        <v>13.49</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>1.35</v>
+        <v>13.49</v>
       </c>
       <c r="N75" s="6">
         <f>J75/M75-1</f>
@@ -5251,41 +5251,41 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +5.0% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>630481</v>
+        <v>550941</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>7898556851084</t>
+          <t>7894488000101</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>GEL INTIMO LUBRIF.TRADICIONAL 200G RILEX</t>
+          <t>FLOCONETES SEGUROS E ABSORVENTES 75UN</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>23.26</v>
+        <v>1.35</v>
       </c>
       <c r="I76" s="5">
         <f>G76*H76</f>
@@ -5296,13 +5296,13 @@
         <v/>
       </c>
       <c r="K76" s="5" t="n">
-        <v>24.89</v>
+        <v>1.35</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>24.89</v>
+        <v>1.35</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>24.89</v>
+        <v>1.35</v>
       </c>
       <c r="N76" s="6">
         <f>J76/M76-1</f>
@@ -5314,28 +5314,28 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>584661</v>
+        <v>630481</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>7898903991951</t>
+          <t>7898556851084</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>GEL LUBRIFICANTE RILEX TRADIOCIONAL 50G</t>
+          <t>GEL INTIMO LUBRIF.TRADICIONAL 200G RILEX</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
@@ -5348,7 +5348,7 @@
         <v>1</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>6.64</v>
+        <v>23.26</v>
       </c>
       <c r="I77" s="5">
         <f>G77*H77</f>
@@ -5359,13 +5359,13 @@
         <v/>
       </c>
       <c r="K77" s="5" t="n">
-        <v>6.57</v>
+        <v>24.89</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>6.57</v>
+        <v>24.89</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>6.57</v>
+        <v>24.89</v>
       </c>
       <c r="N77" s="6">
         <f>J77/M77-1</f>
@@ -5377,28 +5377,28 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +1.1% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>691301</v>
+        <v>584661</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10354</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>7898741951353</t>
+          <t>7898903991951</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>GEL MASSAGEADOR BLUE ICE 240G</t>
+          <t>GEL LUBRIFICANTE RILEX TRADIOCIONAL 50G</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
@@ -5411,7 +5411,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>6.15</v>
+        <v>6.64</v>
       </c>
       <c r="I78" s="5">
         <f>G78*H78</f>
@@ -5422,13 +5422,13 @@
         <v/>
       </c>
       <c r="K78" s="5" t="n">
-        <v>6.15</v>
+        <v>6.57</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>6.15</v>
+        <v>6.57</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>6.150000000000001</v>
+        <v>6.57</v>
       </c>
       <c r="N78" s="6">
         <f>J78/M78-1</f>
@@ -5440,28 +5440,28 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +1.1% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>691801</v>
+        <v>691301</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>10354</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>7898936049612</t>
+          <t>7898741951353</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>GEL MASSAGEM 17 ERVAS 250G POTE</t>
+          <t>GEL MASSAGEADOR BLUE ICE 240G</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
@@ -5474,7 +5474,7 @@
         <v>1</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>4.19</v>
+        <v>6.15</v>
       </c>
       <c r="I79" s="5">
         <f>G79*H79</f>
@@ -5485,13 +5485,13 @@
         <v/>
       </c>
       <c r="K79" s="5" t="n">
-        <v>4.19</v>
+        <v>6.15</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>4.19</v>
+        <v>6.15</v>
       </c>
       <c r="M79" s="5" t="n">
-        <v>4.19</v>
+        <v>6.150000000000001</v>
       </c>
       <c r="N79" s="6">
         <f>J79/M79-1</f>
@@ -5503,41 +5503,41 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>691601</v>
+        <v>691801</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>7193</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>7898936049704</t>
+          <t>7898936049612</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>GEL MASSAGEM ARNICA E COPAIBA 250G POTE</t>
+          <t>GEL MASSAGEM 17 ERVAS 250G POTE</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>3.67</v>
+        <v>4.19</v>
       </c>
       <c r="I80" s="5">
         <f>G80*H80</f>
@@ -5548,13 +5548,13 @@
         <v/>
       </c>
       <c r="K80" s="5" t="n">
-        <v>3.67</v>
+        <v>4.19</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>3.67</v>
+        <v>4.19</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>3.67</v>
+        <v>4.19</v>
       </c>
       <c r="N80" s="6">
         <f>J80/M80-1</f>
@@ -5566,41 +5566,41 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>627931</v>
+        <v>691601</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>8354</t>
+          <t>9398</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>7898741950288</t>
+          <t>7898936049704</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>GEL MASSAGEM COPAIBA 190G FRASCO</t>
+          <t>GEL MASSAGEM ARNICA E COPAIBA 250G POTE</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H81" s="5" t="n">
-        <v>4.36</v>
+        <v>3.67</v>
       </c>
       <c r="I81" s="5">
         <f>G81*H81</f>
@@ -5611,13 +5611,13 @@
         <v/>
       </c>
       <c r="K81" s="5" t="n">
-        <v>4.36</v>
+        <v>3.67</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>4.36</v>
+        <v>3.67</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>4.36</v>
+        <v>3.67</v>
       </c>
       <c r="N81" s="6">
         <f>J81/M81-1</f>
@@ -5629,28 +5629,28 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>627901</v>
+        <v>627931</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>8354</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>7898936049506</t>
+          <t>7898741950288</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>GEL MASSAGEM EXTRA FORTE ANDIROBA 200G</t>
+          <t>GEL MASSAGEM COPAIBA 190G FRASCO</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
@@ -5663,7 +5663,7 @@
         <v>2</v>
       </c>
       <c r="H82" s="5" t="n">
-        <v>4.39</v>
+        <v>4.36</v>
       </c>
       <c r="I82" s="5">
         <f>G82*H82</f>
@@ -5674,13 +5674,13 @@
         <v/>
       </c>
       <c r="K82" s="5" t="n">
-        <v>4.41</v>
+        <v>4.36</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>4.41</v>
+        <v>4.36</v>
       </c>
       <c r="M82" s="5" t="n">
-        <v>4.41</v>
+        <v>4.36</v>
       </c>
       <c r="N82" s="6">
         <f>J82/M82-1</f>
@@ -5692,41 +5692,41 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>627921</v>
+        <v>627901</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7190</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>7898936049278</t>
+          <t>7898936049506</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>GEL MASSAGEM TUBARAO BRANCO 250G POTE</t>
+          <t>GEL MASSAGEM EXTRA FORTE ANDIROBA 200G</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H83" s="5" t="n">
-        <v>3.7</v>
+        <v>4.39</v>
       </c>
       <c r="I83" s="5">
         <f>G83*H83</f>
@@ -5737,13 +5737,13 @@
         <v/>
       </c>
       <c r="K83" s="5" t="n">
-        <v>3.7</v>
+        <v>4.41</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>3.7</v>
+        <v>4.41</v>
       </c>
       <c r="M83" s="5" t="n">
-        <v>3.700000000000001</v>
+        <v>4.41</v>
       </c>
       <c r="N83" s="6">
         <f>J83/M83-1</f>
@@ -5755,41 +5755,41 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>599261</v>
+        <v>627921</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>7899620911840</t>
+          <t>7898936049278</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>GLICENIX (N.S.) 0,91G CX 6 GLICEROL LACTENTE</t>
+          <t>GEL MASSAGEM TUBARAO BRANCO 250G POTE</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H84" s="5" t="n">
-        <v>5.94</v>
+        <v>3.7</v>
       </c>
       <c r="I84" s="5">
         <f>G84*H84</f>
@@ -5800,13 +5800,13 @@
         <v/>
       </c>
       <c r="K84" s="5" t="n">
-        <v>5.79</v>
+        <v>3.7</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>5.79</v>
+        <v>3.7</v>
       </c>
       <c r="M84" s="5" t="n">
-        <v>5.79</v>
+        <v>3.700000000000001</v>
       </c>
       <c r="N84" s="6">
         <f>J84/M84-1</f>
@@ -5818,41 +5818,41 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.6% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>531501</v>
+        <v>599261</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>7894164005406</t>
+          <t>7899620911840</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>HIDRALI 500ML UVA ROXA AIRELA</t>
+          <t>GLICENIX (N.S.) 0,91G CX 6 GLICEROL LACTENTE</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H85" s="5" t="n">
-        <v>8.359999999999999</v>
+        <v>5.94</v>
       </c>
       <c r="I85" s="5">
         <f>G85*H85</f>
@@ -5863,13 +5863,13 @@
         <v/>
       </c>
       <c r="K85" s="5" t="n">
-        <v>8.300000000000001</v>
+        <v>5.79</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>7.97</v>
+        <v>5.79</v>
       </c>
       <c r="M85" s="5" t="n">
-        <v>8.19</v>
+        <v>5.79</v>
       </c>
       <c r="N85" s="6">
         <f>J85/M85-1</f>
@@ -5881,41 +5881,41 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +0.7% (aceito, lim 5%)</t>
+          <t>REAJUSTE +2.6% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>604151</v>
+        <v>531501</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>7894164009473</t>
+          <t>7894164005406</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>HIDRALI PO 28,29G  ENVELOPE CX COM 4 (GUARANÁ)</t>
+          <t>HIDRALI 500ML UVA ROXA AIRELA</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H86" s="5" t="n">
-        <v>8.94</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="I86" s="5">
         <f>G86*H86</f>
@@ -5926,13 +5926,13 @@
         <v/>
       </c>
       <c r="K86" s="5" t="n">
-        <v>8.94</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>8.890000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="M86" s="5" t="n">
-        <v>8.923333333333334</v>
+        <v>8.19</v>
       </c>
       <c r="N86" s="6">
         <f>J86/M86-1</f>
@@ -5944,38 +5944,38 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +0.7% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>602561</v>
+        <v>604151</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>7708</t>
+          <t>7783</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>7894164009466</t>
+          <t>7894164009473</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>HIDRALI PO 28,29G 4ENV LARANJA SOL</t>
+          <t>HIDRALI PO 28,29G  ENVELOPE CX COM 4 (GUARANÁ)</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H87" s="5" t="n">
         <v>8.94</v>
@@ -5989,13 +5989,13 @@
         <v/>
       </c>
       <c r="K87" s="5" t="n">
-        <v>8.6</v>
+        <v>8.94</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>8.6</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M87" s="5" t="n">
-        <v>8.6</v>
+        <v>8.923333333333334</v>
       </c>
       <c r="N87" s="6">
         <f>J87/M87-1</f>
@@ -6007,38 +6007,38 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +4.0% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>604091</v>
+        <v>602561</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>7708</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>7894164009510</t>
+          <t>7894164009466</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>HIDRALI PO NATURAL  UND</t>
+          <t>HIDRALI PO 28,29G 4ENV LARANJA SOL</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H88" s="5" t="n">
         <v>8.94</v>
@@ -6052,13 +6052,13 @@
         <v/>
       </c>
       <c r="K88" s="5" t="n">
-        <v>8.890000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>8.890000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="M88" s="5" t="n">
-        <v>8.890000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="N88" s="6">
         <f>J88/M88-1</f>
@@ -6070,41 +6070,41 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +0.6% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +4.0% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>531561</v>
+        <v>604091</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>7894164006762</t>
+          <t>7894164009510</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>HIDROXIDO ALUMINIO SAB HORTELA 150ML</t>
+          <t>HIDRALI PO NATURAL  UND</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H89" s="5" t="n">
-        <v>7.25</v>
+        <v>8.94</v>
       </c>
       <c r="I89" s="5">
         <f>G89*H89</f>
@@ -6115,13 +6115,13 @@
         <v/>
       </c>
       <c r="K89" s="5" t="n">
-        <v>7.25</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>7.25</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M89" s="5" t="n">
-        <v>7.25</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="N89" s="6">
         <f>J89/M89-1</f>
@@ -6133,41 +6133,41 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +0.6% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>627841</v>
+        <v>531561</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>7897344301527</t>
+          <t>7894164006762</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>ICE GEL 250G POTE</t>
+          <t>HIDROXIDO ALUMINIO SAB HORTELA 150ML</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H90" s="5" t="n">
-        <v>8.1</v>
+        <v>7.25</v>
       </c>
       <c r="I90" s="5">
         <f>G90*H90</f>
@@ -6178,13 +6178,13 @@
         <v/>
       </c>
       <c r="K90" s="5" t="n">
-        <v>8.1</v>
+        <v>7.25</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>8.1</v>
+        <v>7.25</v>
       </c>
       <c r="M90" s="5" t="n">
-        <v>8.1</v>
+        <v>7.25</v>
       </c>
       <c r="N90" s="6">
         <f>J90/M90-1</f>
@@ -6196,41 +6196,41 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>153041</v>
+        <v>627841</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>7898060132297</t>
+          <t>7897344301527</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>INTESTIN 2MG CX 12 COMP</t>
+          <t>ICE GEL 250G POTE</t>
         </is>
       </c>
       <c r="E91" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H91" s="5" t="n">
-        <v>2.08</v>
+        <v>8.1</v>
       </c>
       <c r="I91" s="5">
         <f>G91*H91</f>
@@ -6241,13 +6241,13 @@
         <v/>
       </c>
       <c r="K91" s="5" t="n">
-        <v>2.02</v>
+        <v>8.1</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>2.02</v>
+        <v>8.1</v>
       </c>
       <c r="M91" s="5" t="n">
-        <v>2.02</v>
+        <v>8.1</v>
       </c>
       <c r="N91" s="6">
         <f>J91/M91-1</f>
@@ -6259,41 +6259,41 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.0% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>553601</v>
+        <v>153041</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3581</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>7896523207834</t>
+          <t>7898060132297</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>K-MED GEL BG 25 G</t>
+          <t>INTESTIN 2MG CX 12 COMP</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H92" s="5" t="n">
-        <v>5.67</v>
+        <v>2.08</v>
       </c>
       <c r="I92" s="5">
         <f>G92*H92</f>
@@ -6304,13 +6304,13 @@
         <v/>
       </c>
       <c r="K92" s="5" t="n">
-        <v>6.59</v>
+        <v>2.02</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>2.99</v>
+        <v>2.02</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>5.19</v>
+        <v>2.02</v>
       </c>
       <c r="N92" s="6">
         <f>J92/M92-1</f>
@@ -6322,41 +6322,41 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +3.0% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>3203</v>
+        <v>553601</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>7898953484304</t>
+          <t>7896523207834</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>LAVADOR NASAL COM FRASCO 300ML C/2 BICOS</t>
+          <t>K-MED GEL BG 25 G</t>
         </is>
       </c>
       <c r="E93" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H93" s="5" t="n">
-        <v>11.49</v>
+        <v>5.67</v>
       </c>
       <c r="I93" s="5">
         <f>G93*H93</f>
@@ -6367,13 +6367,13 @@
         <v/>
       </c>
       <c r="K93" s="5" t="n">
-        <v>11.49</v>
+        <v>6.59</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>11.49</v>
+        <v>2.99</v>
       </c>
       <c r="M93" s="5" t="n">
-        <v>11.49</v>
+        <v>5.19</v>
       </c>
       <c r="N93" s="6">
         <f>J93/M93-1</f>
@@ -6385,41 +6385,41 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>546081</v>
+        <v>3203</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>7897947612358</t>
+          <t>7898953484304</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>LAVITAN MEMORIA 60CP</t>
+          <t>LAVADOR NASAL COM FRASCO 300ML C/2 BICOS</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H94" s="5" t="n">
-        <v>14.85</v>
+        <v>11.49</v>
       </c>
       <c r="I94" s="5">
         <f>G94*H94</f>
@@ -6430,13 +6430,13 @@
         <v/>
       </c>
       <c r="K94" s="5" t="n">
-        <v>21.27</v>
+        <v>11.49</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>21.27</v>
+        <v>11.49</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>21.27</v>
+        <v>11.49</v>
       </c>
       <c r="N94" s="6">
         <f>J94/M94-1</f>
@@ -6448,38 +6448,38 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>546481</v>
+        <v>546081</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>7897947600928</t>
+          <t>7897947612358</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>LAVITAN VIT 50+ 60CP</t>
+          <t>LAVITAN MEMORIA 60CP</t>
         </is>
       </c>
       <c r="E95" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H95" s="5" t="n">
         <v>14.85</v>
@@ -6493,13 +6493,13 @@
         <v/>
       </c>
       <c r="K95" s="5" t="n">
-        <v>14.85</v>
+        <v>21.27</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>14.85</v>
+        <v>21.27</v>
       </c>
       <c r="M95" s="5" t="n">
-        <v>14.85</v>
+        <v>21.27</v>
       </c>
       <c r="N95" s="6">
         <f>J95/M95-1</f>
@@ -6511,41 +6511,41 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>627791</v>
+        <v>546481</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>8628</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>7897947617605</t>
+          <t>7897947600928</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>LAVITAN ZMA PERFORMANCE COMP 2 BL X 15</t>
+          <t>LAVITAN VIT 50+ 60CP</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H96" s="5" t="n">
-        <v>13.5</v>
+        <v>14.85</v>
       </c>
       <c r="I96" s="5">
         <f>G96*H96</f>
@@ -6556,13 +6556,13 @@
         <v/>
       </c>
       <c r="K96" s="5" t="n">
-        <v>18.36</v>
+        <v>14.85</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>16.39</v>
+        <v>14.85</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>16.39</v>
+        <v>14.85</v>
       </c>
       <c r="N96" s="6">
         <f>J96/M96-1</f>
@@ -6574,41 +6574,41 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>4083</v>
+        <v>627791</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>8859</t>
+          <t>8628</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>7898575780754</t>
+          <t>7897947617605</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>LEITE DE MAGNESIA 100ML HORTELA</t>
+          <t>LAVITAN ZMA PERFORMANCE COMP 2 BL X 15</t>
         </is>
       </c>
       <c r="E97" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H97" s="5" t="n">
-        <v>1.99</v>
+        <v>13.5</v>
       </c>
       <c r="I97" s="5">
         <f>G97*H97</f>
@@ -6619,13 +6619,13 @@
         <v/>
       </c>
       <c r="K97" s="5" t="n">
-        <v>3.54</v>
+        <v>18.36</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>3.54</v>
+        <v>16.39</v>
       </c>
       <c r="M97" s="5" t="n">
-        <v>3.54</v>
+        <v>16.39</v>
       </c>
       <c r="N97" s="6">
         <f>J97/M97-1</f>
@@ -6637,41 +6637,41 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>646631</v>
+        <v>4083</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>8859</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>7898031310211</t>
+          <t>7898575780754</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>LEITE DE MAGNESIA 120ML TRADICIONAL</t>
+          <t>LEITE DE MAGNESIA 100ML HORTELA</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>5</v>
+        <v>1.99</v>
       </c>
       <c r="I98" s="5">
         <f>G98*H98</f>
@@ -6682,13 +6682,13 @@
         <v/>
       </c>
       <c r="K98" s="5" t="n">
-        <v>5.01</v>
+        <v>3.54</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>5.01</v>
+        <v>3.54</v>
       </c>
       <c r="M98" s="5" t="n">
-        <v>5.01</v>
+        <v>3.54</v>
       </c>
       <c r="N98" s="6">
         <f>J98/M98-1</f>
@@ -6700,41 +6700,41 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>651461</v>
+        <v>646631</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>7615</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>7898179711314</t>
+          <t>7898031310211</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>LEITE DE MAGNESIA GASTRIMEC 100ML TRADIC</t>
+          <t>LEITE DE MAGNESIA 120ML TRADICIONAL</t>
         </is>
       </c>
       <c r="E99" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>4.58</v>
+        <v>5</v>
       </c>
       <c r="I99" s="5">
         <f>G99*H99</f>
@@ -6745,13 +6745,13 @@
         <v/>
       </c>
       <c r="K99" s="5" t="n">
-        <v>4.5</v>
+        <v>5.01</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>4.5</v>
+        <v>5.01</v>
       </c>
       <c r="M99" s="5" t="n">
-        <v>4.5</v>
+        <v>5.01</v>
       </c>
       <c r="N99" s="6">
         <f>J99/M99-1</f>
@@ -6763,41 +6763,41 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +1.8% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>55801</v>
+        <v>651461</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>7898060133904</t>
+          <t>7898179711314</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>LERGIDRIN 0,4+0,05MG/ML XPE FR X 120ML+CM</t>
+          <t>LEITE DE MAGNESIA GASTRIMEC 100ML TRADIC</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>4.5</v>
+        <v>4.58</v>
       </c>
       <c r="I100" s="5">
         <f>G100*H100</f>
@@ -6808,13 +6808,13 @@
         <v/>
       </c>
       <c r="K100" s="5" t="n">
-        <v>4.31</v>
+        <v>4.5</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>4.31</v>
+        <v>4.5</v>
       </c>
       <c r="M100" s="5" t="n">
-        <v>4.31</v>
+        <v>4.5</v>
       </c>
       <c r="N100" s="6">
         <f>J100/M100-1</f>
@@ -6826,41 +6826,41 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +4.4% (aceito, lim 5%)</t>
+          <t>REAJUSTE +1.8% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>151761</v>
+        <v>55801</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>7893454100555</t>
+          <t>7898060133904</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>LIDIAL 50MG/G POM BG 25G</t>
+          <t>LERGIDRIN 0,4+0,05MG/ML XPE FR X 120ML+CM</t>
         </is>
       </c>
       <c r="E101" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>6.95</v>
+        <v>4.5</v>
       </c>
       <c r="I101" s="5">
         <f>G101*H101</f>
@@ -6871,13 +6871,13 @@
         <v/>
       </c>
       <c r="K101" s="5" t="n">
-        <v>6.73</v>
+        <v>4.31</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>6.73</v>
+        <v>4.31</v>
       </c>
       <c r="M101" s="5" t="n">
-        <v>6.73</v>
+        <v>4.31</v>
       </c>
       <c r="N101" s="6">
         <f>J101/M101-1</f>
@@ -6889,41 +6889,41 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.3% (aceito, lim 5%)</t>
+          <t>REAJUSTE +4.4% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>324761</v>
+        <v>151761</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>7896523202822</t>
+          <t>7893454100555</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>LORATAMED 10MG CX 12 COMP</t>
+          <t>LIDIAL 50MG/G POM BG 25G</t>
         </is>
       </c>
       <c r="E102" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>1.76</v>
+        <v>6.95</v>
       </c>
       <c r="I102" s="5">
         <f>G102*H102</f>
@@ -6934,13 +6934,13 @@
         <v/>
       </c>
       <c r="K102" s="5" t="n">
-        <v>1.69</v>
+        <v>6.73</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>1.49</v>
+        <v>6.73</v>
       </c>
       <c r="M102" s="5" t="n">
-        <v>1.556666666666667</v>
+        <v>6.73</v>
       </c>
       <c r="N102" s="6">
         <f>J102/M102-1</f>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +4.1% (aceito, lim 5%)</t>
+          <t>REAJUSTE +3.3% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr"/>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr"/>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +0.5% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +0.5% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr"/>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr"/>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr"/>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr"/>
@@ -7393,7 +7393,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.8% (aceito, lim 5%)</t>
+          <t>REAJUSTE +3.8% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr"/>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr"/>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr"/>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr"/>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr"/>
@@ -7901,41 +7901,41 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>5053</v>
+        <v>605901</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>7508</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>7896544927698</t>
+          <t>7898719040157</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>OLEO DE GIRASSOL DERMA PROTECT 200ML</t>
+          <t>OLEO DE GIRASSOL DERSIN 100ML</t>
         </is>
       </c>
       <c r="E118" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H118" s="5" t="n">
-        <v>5.79</v>
+        <v>5.3</v>
       </c>
       <c r="I118" s="5">
         <f>G118*H118</f>
@@ -7946,13 +7946,13 @@
         <v/>
       </c>
       <c r="K118" s="5" t="n">
-        <v>5.45</v>
+        <v>5.22</v>
       </c>
       <c r="L118" s="5" t="n">
-        <v>5.45</v>
+        <v>5.22</v>
       </c>
       <c r="M118" s="5" t="n">
-        <v>5.45</v>
+        <v>5.22</v>
       </c>
       <c r="N118" s="6">
         <f>J118/M118-1</f>
@@ -7964,41 +7964,41 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +6.2% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +1.5% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>605901</v>
+        <v>613861</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>7508</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>7898719040157</t>
+          <t>7898719040164</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>OLEO DE GIRASSOL DERSIN 100ML</t>
+          <t>OLEO DE GIRASSOL DERSIN 200ML</t>
         </is>
       </c>
       <c r="E119" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H119" s="5" t="n">
-        <v>5.3</v>
+        <v>8.67</v>
       </c>
       <c r="I119" s="5">
         <f>G119*H119</f>
@@ -8009,13 +8009,13 @@
         <v/>
       </c>
       <c r="K119" s="5" t="n">
-        <v>5.22</v>
+        <v>8.67</v>
       </c>
       <c r="L119" s="5" t="n">
-        <v>5.22</v>
+        <v>8.67</v>
       </c>
       <c r="M119" s="5" t="n">
-        <v>5.22</v>
+        <v>8.67</v>
       </c>
       <c r="N119" s="6">
         <f>J119/M119-1</f>
@@ -8027,41 +8027,41 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +1.5% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>613861</v>
+        <v>531661</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>7541</t>
+          <t>153</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>7898719040164</t>
+          <t>7898031310709</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>OLEO DE GIRASSOL DERSIN 200ML</t>
+          <t>PASTA D AGUA 100G</t>
         </is>
       </c>
       <c r="E120" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H120" s="5" t="n">
-        <v>8.67</v>
+        <v>6.28</v>
       </c>
       <c r="I120" s="5">
         <f>G120*H120</f>
@@ -8072,13 +8072,13 @@
         <v/>
       </c>
       <c r="K120" s="5" t="n">
-        <v>8.67</v>
+        <v>6.28</v>
       </c>
       <c r="L120" s="5" t="n">
-        <v>8.67</v>
+        <v>6.13</v>
       </c>
       <c r="M120" s="5" t="n">
-        <v>8.67</v>
+        <v>6.13</v>
       </c>
       <c r="N120" s="6">
         <f>J120/M120-1</f>
@@ -8090,41 +8090,41 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>531661</v>
+        <v>4063</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>7284</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>7898031310709</t>
+          <t>7898031311102</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>PASTA D AGUA 100G</t>
+          <t>PASTA DAGUA SIMPLES 90G BISNAGA</t>
         </is>
       </c>
       <c r="E121" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H121" s="5" t="n">
-        <v>6.28</v>
+        <v>7.74</v>
       </c>
       <c r="I121" s="5">
         <f>G121*H121</f>
@@ -8135,13 +8135,13 @@
         <v/>
       </c>
       <c r="K121" s="5" t="n">
-        <v>6.28</v>
+        <v>7.74</v>
       </c>
       <c r="L121" s="5" t="n">
-        <v>6.13</v>
+        <v>7.57</v>
       </c>
       <c r="M121" s="5" t="n">
-        <v>6.13</v>
+        <v>7.683333333333334</v>
       </c>
       <c r="N121" s="6">
         <f>J121/M121-1</f>
@@ -8160,34 +8160,34 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>4063</v>
+        <v>662241</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>6841</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>7898031311102</t>
+          <t>7898719041048</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>PASTA DAGUA SIMPLES 90G BISNAGA</t>
+          <t>PEDRA HUME 35ML SPRAY</t>
         </is>
       </c>
       <c r="E122" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H122" s="5" t="n">
-        <v>7.74</v>
+        <v>6.59</v>
       </c>
       <c r="I122" s="5">
         <f>G122*H122</f>
@@ -8198,13 +8198,13 @@
         <v/>
       </c>
       <c r="K122" s="5" t="n">
-        <v>7.74</v>
+        <v>6.59</v>
       </c>
       <c r="L122" s="5" t="n">
-        <v>7.57</v>
+        <v>6.59</v>
       </c>
       <c r="M122" s="5" t="n">
-        <v>7.683333333333334</v>
+        <v>6.59</v>
       </c>
       <c r="N122" s="6">
         <f>J122/M122-1</f>
@@ -8223,34 +8223,34 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>662241</v>
+        <v>639911</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>6841</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>7898719041048</t>
+          <t>7898953484410</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>PEDRA HUME 35ML SPRAY</t>
+          <t>PENTE FINO TIRA PIOLHO 1 UN ROSA</t>
         </is>
       </c>
       <c r="E123" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H123" s="5" t="n">
-        <v>6.59</v>
+        <v>11.84</v>
       </c>
       <c r="I123" s="5">
         <f>G123*H123</f>
@@ -8261,13 +8261,13 @@
         <v/>
       </c>
       <c r="K123" s="5" t="n">
-        <v>6.59</v>
+        <v>11.84</v>
       </c>
       <c r="L123" s="5" t="n">
-        <v>6.59</v>
+        <v>11.84</v>
       </c>
       <c r="M123" s="5" t="n">
-        <v>6.59</v>
+        <v>11.84</v>
       </c>
       <c r="N123" s="6">
         <f>J123/M123-1</f>
@@ -8279,41 +8279,41 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>639911</v>
+        <v>547801</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>7898953484410</t>
+          <t>7899620913059</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>PENTE FINO TIRA PIOLHO 1 UN ROSA</t>
+          <t>PERIODENT SOLUCAO BUCAL 250 ML</t>
         </is>
       </c>
       <c r="E124" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H124" s="5" t="n">
-        <v>11.84</v>
+        <v>10.79</v>
       </c>
       <c r="I124" s="5">
         <f>G124*H124</f>
@@ -8324,13 +8324,13 @@
         <v/>
       </c>
       <c r="K124" s="5" t="n">
-        <v>11.84</v>
+        <v>10.79</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>11.84</v>
+        <v>10.79</v>
       </c>
       <c r="M124" s="5" t="n">
-        <v>11.84</v>
+        <v>10.79</v>
       </c>
       <c r="N124" s="6">
         <f>J124/M124-1</f>
@@ -8342,28 +8342,28 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>3563</v>
+        <v>5703</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>6735</t>
+          <t>9657</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>7898719040539</t>
+          <t>609963917563</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>PERIOASSEPT 250ML MENTA COM ALCOOL</t>
+          <t>POLIVITAMINICO AZ C/60 CPS</t>
         </is>
       </c>
       <c r="E125" s="4" t="n">
@@ -8376,7 +8376,7 @@
         <v>1</v>
       </c>
       <c r="H125" s="5" t="n">
-        <v>12.95</v>
+        <v>12.62</v>
       </c>
       <c r="I125" s="5">
         <f>G125*H125</f>
@@ -8386,60 +8386,48 @@
         <f>H125/E125</f>
         <v/>
       </c>
-      <c r="K125" s="5" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="L125" s="5" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="M125" s="5" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="N125" s="6">
-        <f>J125/M125-1</f>
-        <v/>
-      </c>
-      <c r="O125" s="6">
-        <f>J125/K125-1</f>
-        <v/>
-      </c>
+      <c r="K125" s="5" t="n"/>
+      <c r="L125" s="5" t="n"/>
+      <c r="M125" s="5" t="n"/>
+      <c r="N125" s="6" t="n"/>
+      <c r="O125" s="6" t="n"/>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +8.0% (aceito, lim 10% zerado)</t>
+          <t>SEM HISTÓRICO</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>547801</v>
+        <v>588931</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>7899620913059</t>
+          <t>7897146600583</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>PERIODENT SOLUCAO BUCAL 250 ML</t>
+          <t>PRANFIGALDO 10ML ABACAXI UN (FLACONETE)</t>
         </is>
       </c>
       <c r="E126" s="4" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="F126" s="4" t="n">
         <v>2</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H126" s="5" t="n">
-        <v>10.79</v>
+        <v>24.29</v>
       </c>
       <c r="I126" s="5">
         <f>G126*H126</f>
@@ -8450,13 +8438,13 @@
         <v/>
       </c>
       <c r="K126" s="5" t="n">
-        <v>10.79</v>
+        <v>0.4048</v>
       </c>
       <c r="L126" s="5" t="n">
-        <v>10.79</v>
+        <v>0.4048</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>10.79</v>
+        <v>0.4048</v>
       </c>
       <c r="N126" s="6">
         <f>J126/M126-1</f>
@@ -8468,41 +8456,45 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q126" s="2" t="inlineStr"/>
+          <t>OK (≤ últ. compra)</t>
+        </is>
+      </c>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>1 emb = 60 un</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>5703</v>
+        <v>543501</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>9657</t>
+          <t>794</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>609963917563</t>
+          <t>7897146600040</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>POLIVITAMINICO AZ C/60 CPS</t>
+          <t>PRANFIGALDO BOLDO 10ML(FLACONETES)</t>
         </is>
       </c>
       <c r="E127" s="4" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G127" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H127" s="5" t="n">
-        <v>12.62</v>
+        <v>33.75</v>
       </c>
       <c r="I127" s="5">
         <f>G127*H127</f>
@@ -8512,48 +8504,64 @@
         <f>H127/E127</f>
         <v/>
       </c>
-      <c r="K127" s="5" t="n"/>
-      <c r="L127" s="5" t="n"/>
-      <c r="M127" s="5" t="n"/>
-      <c r="N127" s="6" t="n"/>
-      <c r="O127" s="6" t="n"/>
+      <c r="K127" s="5" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>0.5367</v>
+      </c>
+      <c r="M127" s="5" t="n">
+        <v>0.5538999999999999</v>
+      </c>
+      <c r="N127" s="6">
+        <f>J127/M127-1</f>
+        <v/>
+      </c>
+      <c r="O127" s="6">
+        <f>J127/K127-1</f>
+        <v/>
+      </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>SEM HISTÓRICO</t>
-        </is>
-      </c>
-      <c r="Q127" s="2" t="inlineStr"/>
+          <t>OK (≤ últ. compra)</t>
+        </is>
+      </c>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>1 emb = 60 un</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>588931</v>
+        <v>550161</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>7897146600583</t>
+          <t>7898556850209</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>PRANFIGALDO 10ML ABACAXI UN (FLACONETE)</t>
+          <t>PRES RILEX TEXTURIZADO 3UN</t>
         </is>
       </c>
       <c r="E128" s="4" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G128" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H128" s="5" t="n">
-        <v>24.29</v>
+        <v>4.73</v>
       </c>
       <c r="I128" s="5">
         <f>G128*H128</f>
@@ -8564,13 +8572,13 @@
         <v/>
       </c>
       <c r="K128" s="5" t="n">
-        <v>0.4048</v>
+        <v>4.56</v>
       </c>
       <c r="L128" s="5" t="n">
-        <v>0.4048</v>
+        <v>4.55</v>
       </c>
       <c r="M128" s="5" t="n">
-        <v>0.4048</v>
+        <v>4.553333333333334</v>
       </c>
       <c r="N128" s="6">
         <f>J128/M128-1</f>
@@ -8582,45 +8590,41 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q128" s="2" t="inlineStr">
-        <is>
-          <t>1 emb = 60 un</t>
-        </is>
-      </c>
+          <t>REAJUSTE +3.7% vs últ. (≤4%)</t>
+        </is>
+      </c>
+      <c r="Q128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>543501</v>
+        <v>584461</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>5736</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>7897146600040</t>
+          <t>7898556850452</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>PRANFIGALDO BOLDO 10ML(FLACONETES)</t>
+          <t>PRESERVATIVO RILEX LEITE CONDENSADO 3UN</t>
         </is>
       </c>
       <c r="E129" s="4" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F129" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G129" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H129" s="5" t="n">
-        <v>33.75</v>
+        <v>2.33</v>
       </c>
       <c r="I129" s="5">
         <f>G129*H129</f>
@@ -8631,13 +8635,13 @@
         <v/>
       </c>
       <c r="K129" s="5" t="n">
-        <v>0.5625</v>
+        <v>2.22</v>
       </c>
       <c r="L129" s="5" t="n">
-        <v>0.5367</v>
+        <v>2.22</v>
       </c>
       <c r="M129" s="5" t="n">
-        <v>0.5538999999999999</v>
+        <v>2.22</v>
       </c>
       <c r="N129" s="6">
         <f>J129/M129-1</f>
@@ -8649,45 +8653,41 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
-        </is>
-      </c>
-      <c r="Q129" s="2" t="inlineStr">
-        <is>
-          <t>1 emb = 60 un</t>
-        </is>
-      </c>
+          <t>REAJUSTE +5.0% vs média (≤6%)</t>
+        </is>
+      </c>
+      <c r="Q129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>550201</v>
+        <v>532801</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>4713</t>
+          <t>879</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>7898556850254</t>
+          <t>7898903991487</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>PRES RILEX HOT 3UN</t>
+          <t>PRESERVATIVO RILEX LUBRIFICADO C/3</t>
         </is>
       </c>
       <c r="E130" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H130" s="5" t="n">
-        <v>5.3</v>
+        <v>2.17</v>
       </c>
       <c r="I130" s="5">
         <f>G130*H130</f>
@@ -8698,13 +8698,13 @@
         <v/>
       </c>
       <c r="K130" s="5" t="n">
-        <v>5.07</v>
+        <v>2.11</v>
       </c>
       <c r="L130" s="5" t="n">
-        <v>4.85</v>
+        <v>2.09</v>
       </c>
       <c r="M130" s="5" t="n">
-        <v>4.996666666666667</v>
+        <v>2.096666666666666</v>
       </c>
       <c r="N130" s="6">
         <f>J130/M130-1</f>
@@ -8716,28 +8716,28 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +4.5% (aceito, lim 5%)</t>
+          <t>REAJUSTE +2.8% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>550161</v>
+        <v>532821</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>882</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>7898556850209</t>
+          <t>7898903991517</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>PRES RILEX TEXTURIZADO 3UN</t>
+          <t>PRESERVATIVO RILEX MORANGO C/3</t>
         </is>
       </c>
       <c r="E131" s="4" t="n">
@@ -8750,7 +8750,7 @@
         <v>1</v>
       </c>
       <c r="H131" s="5" t="n">
-        <v>4.73</v>
+        <v>2.21</v>
       </c>
       <c r="I131" s="5">
         <f>G131*H131</f>
@@ -8761,13 +8761,13 @@
         <v/>
       </c>
       <c r="K131" s="5" t="n">
-        <v>4.56</v>
+        <v>2.14</v>
       </c>
       <c r="L131" s="5" t="n">
-        <v>4.55</v>
+        <v>2.13</v>
       </c>
       <c r="M131" s="5" t="n">
-        <v>4.553333333333334</v>
+        <v>2.133333333333333</v>
       </c>
       <c r="N131" s="6">
         <f>J131/M131-1</f>
@@ -8779,41 +8779,41 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.7% (aceito, lim 5%)</t>
+          <t>REAJUSTE +3.3% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>584461</v>
+        <v>532781</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>5736</t>
+          <t>877</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>7898556850452</t>
+          <t>7898556850193</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>PRESERVATIVO RILEX LEITE CONDENSADO 3UN</t>
+          <t>PRESERVATIVO RILEX SENSITIVE C/3</t>
         </is>
       </c>
       <c r="E132" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H132" s="5" t="n">
-        <v>2.33</v>
+        <v>4.55</v>
       </c>
       <c r="I132" s="5">
         <f>G132*H132</f>
@@ -8824,13 +8824,13 @@
         <v/>
       </c>
       <c r="K132" s="5" t="n">
-        <v>2.22</v>
+        <v>4.38</v>
       </c>
       <c r="L132" s="5" t="n">
-        <v>2.22</v>
+        <v>4.37</v>
       </c>
       <c r="M132" s="5" t="n">
-        <v>2.22</v>
+        <v>4.373333333333334</v>
       </c>
       <c r="N132" s="6">
         <f>J132/M132-1</f>
@@ -8842,41 +8842,41 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +5.0% (aceito, lim 5%)</t>
+          <t>REAJUSTE +3.9% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>532801</v>
+        <v>68841</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>7898903991487</t>
+          <t>7896004765709</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>PRESERVATIVO RILEX LUBRIFICADO C/3</t>
+          <t>PV - INALIDE 64MPV - CG SUS SPR NAS FR 120 ACION</t>
         </is>
       </c>
       <c r="E133" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G133" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H133" s="5" t="n">
-        <v>2.17</v>
+        <v>20.33</v>
       </c>
       <c r="I133" s="5">
         <f>G133*H133</f>
@@ -8887,13 +8887,13 @@
         <v/>
       </c>
       <c r="K133" s="5" t="n">
-        <v>2.11</v>
+        <v>23.98</v>
       </c>
       <c r="L133" s="5" t="n">
-        <v>2.09</v>
+        <v>23.98</v>
       </c>
       <c r="M133" s="5" t="n">
-        <v>2.096666666666666</v>
+        <v>23.98</v>
       </c>
       <c r="N133" s="6">
         <f>J133/M133-1</f>
@@ -8905,28 +8905,28 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.8% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>532821</v>
+        <v>1353</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>8774</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>7898903991517</t>
+          <t>7898714761477</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>PRESERVATIVO RILEX MORANGO C/3</t>
+          <t>PV K2+D3 CAPS REV X 30</t>
         </is>
       </c>
       <c r="E134" s="4" t="n">
@@ -8939,7 +8939,7 @@
         <v>1</v>
       </c>
       <c r="H134" s="5" t="n">
-        <v>2.21</v>
+        <v>20.61</v>
       </c>
       <c r="I134" s="5">
         <f>G134*H134</f>
@@ -8950,13 +8950,13 @@
         <v/>
       </c>
       <c r="K134" s="5" t="n">
-        <v>2.14</v>
+        <v>41.8867</v>
       </c>
       <c r="L134" s="5" t="n">
-        <v>2.13</v>
+        <v>41.8867</v>
       </c>
       <c r="M134" s="5" t="n">
-        <v>2.133333333333333</v>
+        <v>41.8867</v>
       </c>
       <c r="N134" s="6">
         <f>J134/M134-1</f>
@@ -8968,41 +8968,45 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.3% (aceito, lim 5%)</t>
-        </is>
-      </c>
-      <c r="Q134" s="2" t="inlineStr"/>
+          <t>OK (≤ últ. compra)</t>
+        </is>
+      </c>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>conferir emb.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>532781</v>
+        <v>419001</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>4865</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>7898556850193</t>
+          <t>7898569763916</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>PRESERVATIVO RILEX SENSITIVE C/3</t>
+          <t>RISEDRONATO SODICO 150MG CX 1 COMP REV</t>
         </is>
       </c>
       <c r="E135" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G135" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H135" s="5" t="n">
-        <v>4.55</v>
+        <v>9.99</v>
       </c>
       <c r="I135" s="5">
         <f>G135*H135</f>
@@ -9013,13 +9017,13 @@
         <v/>
       </c>
       <c r="K135" s="5" t="n">
-        <v>4.38</v>
+        <v>18.43</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>4.37</v>
+        <v>13.5</v>
       </c>
       <c r="M135" s="5" t="n">
-        <v>4.373333333333334</v>
+        <v>13.5</v>
       </c>
       <c r="N135" s="6">
         <f>J135/M135-1</f>
@@ -9031,41 +9035,41 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.9% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>68841</v>
+        <v>234</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>528</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>7896004765709</t>
+          <t>7898277711421</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>PV - INALIDE 64MPV - CG SUS SPR NAS FR 120 ACION</t>
+          <t>SAB DE COCO BARRA 100G</t>
         </is>
       </c>
       <c r="E136" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H136" s="5" t="n">
-        <v>20.33</v>
+        <v>5.74</v>
       </c>
       <c r="I136" s="5">
         <f>G136*H136</f>
@@ -9075,60 +9079,48 @@
         <f>H136/E136</f>
         <v/>
       </c>
-      <c r="K136" s="5" t="n">
-        <v>23.98</v>
-      </c>
-      <c r="L136" s="5" t="n">
-        <v>23.98</v>
-      </c>
-      <c r="M136" s="5" t="n">
-        <v>23.98</v>
-      </c>
-      <c r="N136" s="6">
-        <f>J136/M136-1</f>
-        <v/>
-      </c>
-      <c r="O136" s="6">
-        <f>J136/K136-1</f>
-        <v/>
-      </c>
+      <c r="K136" s="5" t="n"/>
+      <c r="L136" s="5" t="n"/>
+      <c r="M136" s="5" t="n"/>
+      <c r="N136" s="6" t="n"/>
+      <c r="O136" s="6" t="n"/>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>SEM HISTÓRICO</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>1353</v>
+        <v>674361</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>8774</t>
+          <t>7213</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>7898714761477</t>
+          <t>7898936049049</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>PV K2+D3 CAPS REV X 30</t>
+          <t>SABONETE INTIMO 17 ERVAS 210ML</t>
         </is>
       </c>
       <c r="E137" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G137" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H137" s="5" t="n">
-        <v>20.61</v>
+        <v>3.33</v>
       </c>
       <c r="I137" s="5">
         <f>G137*H137</f>
@@ -9139,13 +9131,13 @@
         <v/>
       </c>
       <c r="K137" s="5" t="n">
-        <v>41.8867</v>
+        <v>3.35</v>
       </c>
       <c r="L137" s="5" t="n">
-        <v>41.8867</v>
+        <v>3.35</v>
       </c>
       <c r="M137" s="5" t="n">
-        <v>41.8867</v>
+        <v>3.35</v>
       </c>
       <c r="N137" s="6">
         <f>J137/M137-1</f>
@@ -9157,32 +9149,28 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q137" s="2" t="inlineStr">
-        <is>
-          <t>conferir emb.</t>
-        </is>
-      </c>
+          <t>OK (≤ últ. compra)</t>
+        </is>
+      </c>
+      <c r="Q137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>622411</v>
+        <v>1503</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>7206</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>7898582291854</t>
+          <t>7898936049735</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>QUEIMADOL POMADA 30G</t>
+          <t>SABONETE INTIMO BARBATIMAO AROEIRA 210ML</t>
         </is>
       </c>
       <c r="E138" s="4" t="n">
@@ -9195,7 +9183,7 @@
         <v>3</v>
       </c>
       <c r="H138" s="5" t="n">
-        <v>12.34</v>
+        <v>3.36</v>
       </c>
       <c r="I138" s="5">
         <f>G138*H138</f>
@@ -9206,13 +9194,13 @@
         <v/>
       </c>
       <c r="K138" s="5" t="n">
-        <v>11.52</v>
+        <v>3.38</v>
       </c>
       <c r="L138" s="5" t="n">
-        <v>11.52</v>
+        <v>3.38</v>
       </c>
       <c r="M138" s="5" t="n">
-        <v>11.52</v>
+        <v>3.38</v>
       </c>
       <c r="N138" s="6">
         <f>J138/M138-1</f>
@@ -9224,41 +9212,41 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +7.1% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>5603</v>
+        <v>531721</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>9721</t>
+          <t>157</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>7898767761684</t>
+          <t>7898031311324</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>REHIDRAX PO C/04 ENVE AGUA DE COCO</t>
+          <t>SAL AMARGO 30G</t>
         </is>
       </c>
       <c r="E139" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G139" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H139" s="5" t="n">
-        <v>8.76</v>
+        <v>2.36</v>
       </c>
       <c r="I139" s="5">
         <f>G139*H139</f>
@@ -9269,13 +9257,13 @@
         <v/>
       </c>
       <c r="K139" s="5" t="n">
-        <v>8.07</v>
+        <v>2.49</v>
       </c>
       <c r="L139" s="5" t="n">
-        <v>8.07</v>
+        <v>2.23</v>
       </c>
       <c r="M139" s="5" t="n">
-        <v>8.07</v>
+        <v>2.316666666666667</v>
       </c>
       <c r="N139" s="6">
         <f>J139/M139-1</f>
@@ -9287,41 +9275,41 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +8.6% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>5903</v>
+        <v>639041</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>9719</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>7898767761707</t>
+          <t>7898259496001</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>REHIDRAX PO C/04 ENVE LARANJA</t>
+          <t>SERINGA 20ML LL AGULHA 0,7X25</t>
         </is>
       </c>
       <c r="E140" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="H140" s="5" t="n">
-        <v>8.76</v>
+        <v>0.57</v>
       </c>
       <c r="I140" s="5">
         <f>G140*H140</f>
@@ -9332,13 +9320,13 @@
         <v/>
       </c>
       <c r="K140" s="5" t="n">
-        <v>8.07</v>
+        <v>0.64</v>
       </c>
       <c r="L140" s="5" t="n">
-        <v>8.07</v>
+        <v>0.64</v>
       </c>
       <c r="M140" s="5" t="n">
-        <v>8.07</v>
+        <v>0.64</v>
       </c>
       <c r="N140" s="6">
         <f>J140/M140-1</f>
@@ -9350,41 +9338,41 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +8.6% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>419001</v>
+        <v>619851</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>4865</t>
+          <t>3550</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>7898569763916</t>
+          <t>7899620912441</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>RISEDRONATO SODICO 150MG CX 1 COMP REV</t>
+          <t>SIMETICONA (N.S.) 40MG CX 20 COMP</t>
         </is>
       </c>
       <c r="E141" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G141" s="4" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H141" s="5" t="n">
-        <v>9.99</v>
+        <v>2.97</v>
       </c>
       <c r="I141" s="5">
         <f>G141*H141</f>
@@ -9395,13 +9383,13 @@
         <v/>
       </c>
       <c r="K141" s="5" t="n">
-        <v>18.43</v>
+        <v>2.97</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>13.5</v>
+        <v>2.97</v>
       </c>
       <c r="M141" s="5" t="n">
-        <v>13.5</v>
+        <v>2.97</v>
       </c>
       <c r="N141" s="6">
         <f>J141/M141-1</f>
@@ -9413,41 +9401,41 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>234</v>
+        <v>614021</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>7898277711421</t>
+          <t>7897732608146</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>SAB DE COCO BARRA 100G</t>
+          <t>SORALYT 450ML SABOR MORANGO</t>
         </is>
       </c>
       <c r="E142" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G142" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H142" s="5" t="n">
-        <v>5.74</v>
+        <v>6.67</v>
       </c>
       <c r="I142" s="5">
         <f>G142*H142</f>
@@ -9457,48 +9445,60 @@
         <f>H142/E142</f>
         <v/>
       </c>
-      <c r="K142" s="5" t="n"/>
-      <c r="L142" s="5" t="n"/>
-      <c r="M142" s="5" t="n"/>
-      <c r="N142" s="6" t="n"/>
-      <c r="O142" s="6" t="n"/>
+      <c r="K142" s="5" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="M142" s="5" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="N142" s="6">
+        <f>J142/M142-1</f>
+        <v/>
+      </c>
+      <c r="O142" s="6">
+        <f>J142/K142-1</f>
+        <v/>
+      </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>SEM HISTÓRICO</t>
+          <t>REAJUSTE +1.8% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>674361</v>
+        <v>531861</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>7213</t>
+          <t>809</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>7898936049049</t>
+          <t>7898031310389</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>SABONETE INTIMO 17 ERVAS 210ML</t>
+          <t>SORO FISIOLOGICO 9% 100ML</t>
         </is>
       </c>
       <c r="E143" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>7</v>
+        <v>103</v>
       </c>
       <c r="G143" s="4" t="n">
-        <v>7</v>
+        <v>103</v>
       </c>
       <c r="H143" s="5" t="n">
-        <v>3.33</v>
+        <v>2.28</v>
       </c>
       <c r="I143" s="5">
         <f>G143*H143</f>
@@ -9509,13 +9509,13 @@
         <v/>
       </c>
       <c r="K143" s="5" t="n">
-        <v>3.35</v>
+        <v>2.27</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>3.35</v>
+        <v>2.0228</v>
       </c>
       <c r="M143" s="5" t="n">
-        <v>3.35</v>
+        <v>2.094266666666666</v>
       </c>
       <c r="N143" s="6">
         <f>J143/M143-1</f>
@@ -9527,41 +9527,41 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +0.4% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>1503</v>
+        <v>616441</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>7898936049735</t>
+          <t>7896523201542</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>SABONETE INTIMO BARBATIMAO AROEIRA 210ML</t>
+          <t>SUCCINATO METOPROLOL 100MG CX 30 COMP REV</t>
         </is>
       </c>
       <c r="E144" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G144" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H144" s="5" t="n">
-        <v>3.36</v>
+        <v>0.01</v>
       </c>
       <c r="I144" s="5">
         <f>G144*H144</f>
@@ -9572,13 +9572,13 @@
         <v/>
       </c>
       <c r="K144" s="5" t="n">
-        <v>3.38</v>
+        <v>18.99</v>
       </c>
       <c r="L144" s="5" t="n">
-        <v>3.38</v>
+        <v>17.03</v>
       </c>
       <c r="M144" s="5" t="n">
-        <v>3.38</v>
+        <v>18.23666666666667</v>
       </c>
       <c r="N144" s="6">
         <f>J144/M144-1</f>
@@ -9590,41 +9590,45 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q144" s="2" t="inlineStr"/>
+          <t>OK (≤ últ. compra)</t>
+        </is>
+      </c>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>conferir emb.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>531721</v>
+        <v>691001</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>7898031311324</t>
+          <t>7898575780792</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>SAL AMARGO 30G</t>
+          <t>SULFATO FERROSO 125MG 120ML SUS..</t>
         </is>
       </c>
       <c r="E145" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G145" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H145" s="5" t="n">
-        <v>2.36</v>
+        <v>4.04</v>
       </c>
       <c r="I145" s="5">
         <f>G145*H145</f>
@@ -9635,13 +9639,13 @@
         <v/>
       </c>
       <c r="K145" s="5" t="n">
-        <v>2.49</v>
+        <v>4.04</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>2.23</v>
+        <v>4.04</v>
       </c>
       <c r="M145" s="5" t="n">
-        <v>2.316666666666667</v>
+        <v>4.04</v>
       </c>
       <c r="N145" s="6">
         <f>J145/M145-1</f>
@@ -9660,34 +9664,34 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>432121</v>
+        <v>3593</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>8743</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>7898060138220</t>
+          <t>7898575780808</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>SECNIMAX 1000MG CX 2 COMP</t>
+          <t>SULFATO FERROSO 125MG 30ML GTS</t>
         </is>
       </c>
       <c r="E146" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>134</v>
+        <v>3</v>
       </c>
       <c r="G146" s="4" t="n">
-        <v>134</v>
+        <v>3</v>
       </c>
       <c r="H146" s="5" t="n">
-        <v>2.61</v>
+        <v>2.69</v>
       </c>
       <c r="I146" s="5">
         <f>G146*H146</f>
@@ -9698,13 +9702,13 @@
         <v/>
       </c>
       <c r="K146" s="5" t="n">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="L146" s="5" t="n">
-        <v>2.39</v>
+        <v>2.69</v>
       </c>
       <c r="M146" s="5" t="n">
-        <v>2.39</v>
+        <v>2.69</v>
       </c>
       <c r="N146" s="6">
         <f>J146/M146-1</f>
@@ -9716,41 +9720,41 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +4.8% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>639041</v>
+        <v>548381</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>7222</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>7898259496001</t>
+          <t>7897146600255</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>SERINGA 20ML LL AGULHA 0,7X25</t>
+          <t>SULFATO FERROSO 200MG C/50 CPR</t>
         </is>
       </c>
       <c r="E147" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="H147" s="5" t="n">
-        <v>0.57</v>
+        <v>4.37</v>
       </c>
       <c r="I147" s="5">
         <f>G147*H147</f>
@@ -9761,13 +9765,13 @@
         <v/>
       </c>
       <c r="K147" s="5" t="n">
-        <v>0.64</v>
+        <v>4.37</v>
       </c>
       <c r="L147" s="5" t="n">
-        <v>0.64</v>
+        <v>4.37</v>
       </c>
       <c r="M147" s="5" t="n">
-        <v>0.64</v>
+        <v>4.37</v>
       </c>
       <c r="N147" s="6">
         <f>J147/M147-1</f>
@@ -9779,41 +9783,41 @@
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>619851</v>
+        <v>612291</v>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>3550</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>7899620912441</t>
+          <t>7894164005802</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>SIMETICONA (N.S.) 40MG CX 20 COMP</t>
+          <t>SULFERMAX GTS 30ML (SULFATO FERROSO)</t>
         </is>
       </c>
       <c r="E148" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G148" s="4" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H148" s="5" t="n">
-        <v>2.97</v>
+        <v>3.29</v>
       </c>
       <c r="I148" s="5">
         <f>G148*H148</f>
@@ -9824,13 +9828,13 @@
         <v/>
       </c>
       <c r="K148" s="5" t="n">
-        <v>2.97</v>
+        <v>3.17</v>
       </c>
       <c r="L148" s="5" t="n">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="M148" s="5" t="n">
-        <v>2.97</v>
+        <v>3.123333333333334</v>
       </c>
       <c r="N148" s="6">
         <f>J148/M148-1</f>
@@ -9842,41 +9846,41 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +3.8% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>614021</v>
+        <v>578801</v>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>7897732608146</t>
+          <t>7898301056986</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>SORALYT 450ML SABOR MORANGO</t>
+          <t>TERMOMETRO DIGITAL CLINICO TH150 LARANJA</t>
         </is>
       </c>
       <c r="E149" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G149" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H149" s="5" t="n">
-        <v>6.67</v>
+        <v>11.88</v>
       </c>
       <c r="I149" s="5">
         <f>G149*H149</f>
@@ -9887,13 +9891,13 @@
         <v/>
       </c>
       <c r="K149" s="5" t="n">
-        <v>6.55</v>
+        <v>12.59</v>
       </c>
       <c r="L149" s="5" t="n">
-        <v>6.55</v>
+        <v>12.59</v>
       </c>
       <c r="M149" s="5" t="n">
-        <v>6.55</v>
+        <v>12.59</v>
       </c>
       <c r="N149" s="6">
         <f>J149/M149-1</f>
@@ -9905,41 +9909,41 @@
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +1.8% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>531861</v>
+        <v>543341</v>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>7898031310389</t>
+          <t>7898301056979</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>SORO FISIOLOGICO 9% 100ML</t>
+          <t>TERMOMETRO DIGITAL G-TECH ROSA UNIDADE</t>
         </is>
       </c>
       <c r="E150" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>103</v>
+        <v>1</v>
       </c>
       <c r="G150" s="4" t="n">
-        <v>103</v>
+        <v>1</v>
       </c>
       <c r="H150" s="5" t="n">
-        <v>2.28</v>
+        <v>13.33</v>
       </c>
       <c r="I150" s="5">
         <f>G150*H150</f>
@@ -9950,13 +9954,13 @@
         <v/>
       </c>
       <c r="K150" s="5" t="n">
-        <v>2.27</v>
+        <v>12.59</v>
       </c>
       <c r="L150" s="5" t="n">
-        <v>2.0228</v>
+        <v>12.59</v>
       </c>
       <c r="M150" s="5" t="n">
-        <v>2.094266666666666</v>
+        <v>12.59</v>
       </c>
       <c r="N150" s="6">
         <f>J150/M150-1</f>
@@ -9968,28 +9972,28 @@
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +0.4% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +5.9% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>616441</v>
+        <v>543361</v>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>7896523201542</t>
+          <t>7898301056962</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>SUCCINATO METOPROLOL 100MG CX 30 COMP REV</t>
+          <t>TERMÔMETRO DIGITAL G-TECH COM PONTA RIGIDA THGTH150V - VERDE</t>
         </is>
       </c>
       <c r="E151" s="4" t="n">
@@ -10002,7 +10006,7 @@
         <v>1</v>
       </c>
       <c r="H151" s="5" t="n">
-        <v>0.01</v>
+        <v>13.33</v>
       </c>
       <c r="I151" s="5">
         <f>G151*H151</f>
@@ -10013,13 +10017,13 @@
         <v/>
       </c>
       <c r="K151" s="5" t="n">
-        <v>18.99</v>
+        <v>12.59</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>17.03</v>
+        <v>12.59</v>
       </c>
       <c r="M151" s="5" t="n">
-        <v>18.23666666666667</v>
+        <v>12.59</v>
       </c>
       <c r="N151" s="6">
         <f>J151/M151-1</f>
@@ -10031,45 +10035,41 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q151" s="2" t="inlineStr">
-        <is>
-          <t>conferir emb.</t>
-        </is>
-      </c>
+          <t>REAJUSTE +5.9% vs média (≤6%)</t>
+        </is>
+      </c>
+      <c r="Q151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>691001</v>
+        <v>532641</v>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>271</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>7898575780792</t>
+          <t>7898126050022</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>SULFATO FERROSO 125MG 120ML SUS..</t>
+          <t>TESTE CONFIRME C/01 UND</t>
         </is>
       </c>
       <c r="E152" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G152" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H152" s="5" t="n">
-        <v>4.04</v>
+        <v>1.69</v>
       </c>
       <c r="I152" s="5">
         <f>G152*H152</f>
@@ -10080,13 +10080,13 @@
         <v/>
       </c>
       <c r="K152" s="5" t="n">
-        <v>4.04</v>
+        <v>1.69</v>
       </c>
       <c r="L152" s="5" t="n">
-        <v>4.04</v>
+        <v>1.69</v>
       </c>
       <c r="M152" s="5" t="n">
-        <v>4.04</v>
+        <v>1.69</v>
       </c>
       <c r="N152" s="6">
         <f>J152/M152-1</f>
@@ -10098,41 +10098,41 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>3593</v>
+        <v>640411</v>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>8743</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>7898575780808</t>
+          <t>7898126050220</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>SULFATO FERROSO 125MG 30ML GTS</t>
+          <t>TESTE GRAVIDEZ CONFIRME SEMANAS TIRA C/1</t>
         </is>
       </c>
       <c r="E153" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G153" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H153" s="5" t="n">
-        <v>2.69</v>
+        <v>7.71</v>
       </c>
       <c r="I153" s="5">
         <f>G153*H153</f>
@@ -10143,13 +10143,13 @@
         <v/>
       </c>
       <c r="K153" s="5" t="n">
-        <v>2.69</v>
+        <v>10.85</v>
       </c>
       <c r="L153" s="5" t="n">
-        <v>2.69</v>
+        <v>10.85</v>
       </c>
       <c r="M153" s="5" t="n">
-        <v>2.69</v>
+        <v>10.85</v>
       </c>
       <c r="N153" s="6">
         <f>J153/M153-1</f>
@@ -10161,41 +10161,41 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>548381</v>
+        <v>461941</v>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>7897146600255</t>
+          <t>7893454100715</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>SULFATO FERROSO 200MG C/50 CPR</t>
+          <t>TIADOL 50MG/G POM DERM BG 20G</t>
         </is>
       </c>
       <c r="E154" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G154" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H154" s="5" t="n">
-        <v>4.37</v>
+        <v>13.89</v>
       </c>
       <c r="I154" s="5">
         <f>G154*H154</f>
@@ -10206,13 +10206,13 @@
         <v/>
       </c>
       <c r="K154" s="5" t="n">
-        <v>4.37</v>
+        <v>13.36</v>
       </c>
       <c r="L154" s="5" t="n">
-        <v>4.37</v>
+        <v>13.36</v>
       </c>
       <c r="M154" s="5" t="n">
-        <v>4.37</v>
+        <v>13.36</v>
       </c>
       <c r="N154" s="6">
         <f>J154/M154-1</f>
@@ -10224,41 +10224,41 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +4.0% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>612291</v>
+        <v>540941</v>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>177</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>7894164005802</t>
+          <t>7898031310952</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>SULFERMAX GTS 30ML (SULFATO FERROSO)</t>
+          <t>TINTURA DE ARNICA 30ML</t>
         </is>
       </c>
       <c r="E155" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G155" s="4" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H155" s="5" t="n">
-        <v>3.29</v>
+        <v>4.31</v>
       </c>
       <c r="I155" s="5">
         <f>G155*H155</f>
@@ -10269,13 +10269,13 @@
         <v/>
       </c>
       <c r="K155" s="5" t="n">
-        <v>3.17</v>
+        <v>4.31</v>
       </c>
       <c r="L155" s="5" t="n">
-        <v>3.08</v>
+        <v>4.31</v>
       </c>
       <c r="M155" s="5" t="n">
-        <v>3.123333333333334</v>
+        <v>4.31</v>
       </c>
       <c r="N155" s="6">
         <f>J155/M155-1</f>
@@ -10287,28 +10287,28 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.8% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>601291</v>
+        <v>18001</v>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>7898301056955</t>
+          <t>7896004739083</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>TERMOMETRO CLIN. DIG. AZUL G-TECH</t>
+          <t>TREXACONT 250MG 1BL X 12 COMP</t>
         </is>
       </c>
       <c r="E156" s="4" t="n">
@@ -10321,7 +10321,7 @@
         <v>1</v>
       </c>
       <c r="H156" s="5" t="n">
-        <v>13.33</v>
+        <v>35.81</v>
       </c>
       <c r="I156" s="5">
         <f>G156*H156</f>
@@ -10332,13 +10332,13 @@
         <v/>
       </c>
       <c r="K156" s="5" t="n">
-        <v>12.56</v>
+        <v>40.53</v>
       </c>
       <c r="L156" s="5" t="n">
-        <v>12.56</v>
+        <v>40.53</v>
       </c>
       <c r="M156" s="5" t="n">
-        <v>12.56</v>
+        <v>40.53</v>
       </c>
       <c r="N156" s="6">
         <f>J156/M156-1</f>
@@ -10350,32 +10350,32 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +6.1% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>578801</v>
+        <v>563961</v>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>395</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>7898301056986</t>
+          <t>7898100243945</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>TERMOMETRO DIGITAL CLINICO TH150 LARANJA</t>
+          <t>TYFLEN 500MG CARTELA COM 10CP</t>
         </is>
       </c>
       <c r="E157" s="4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F157" s="4" t="n">
         <v>1</v>
@@ -10384,7 +10384,7 @@
         <v>1</v>
       </c>
       <c r="H157" s="5" t="n">
-        <v>11.88</v>
+        <v>29.55</v>
       </c>
       <c r="I157" s="5">
         <f>G157*H157</f>
@@ -10395,13 +10395,13 @@
         <v/>
       </c>
       <c r="K157" s="5" t="n">
-        <v>12.59</v>
+        <v>1.8355</v>
       </c>
       <c r="L157" s="5" t="n">
-        <v>12.59</v>
+        <v>1.8355</v>
       </c>
       <c r="M157" s="5" t="n">
-        <v>12.59</v>
+        <v>1.8355</v>
       </c>
       <c r="N157" s="6">
         <f>J157/M157-1</f>
@@ -10413,41 +10413,45 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q157" s="2" t="inlineStr"/>
+          <t>OK (≤ últ. compra)</t>
+        </is>
+      </c>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>1 emb = 20 un</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>543341</v>
+        <v>565801</v>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>7898301056979</t>
+          <t>7898031310600</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>TERMOMETRO DIGITAL G-TECH ROSA UNIDADE</t>
+          <t>UNISSEPT ALCOOL GEL ANTISSEPTICO 450G</t>
         </is>
       </c>
       <c r="E158" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G158" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H158" s="5" t="n">
-        <v>13.33</v>
+        <v>13.08</v>
       </c>
       <c r="I158" s="5">
         <f>G158*H158</f>
@@ -10458,13 +10462,13 @@
         <v/>
       </c>
       <c r="K158" s="5" t="n">
-        <v>12.59</v>
+        <v>13.08</v>
       </c>
       <c r="L158" s="5" t="n">
-        <v>12.59</v>
+        <v>12.51</v>
       </c>
       <c r="M158" s="5" t="n">
-        <v>12.59</v>
+        <v>12.70333333333333</v>
       </c>
       <c r="N158" s="6">
         <f>J158/M158-1</f>
@@ -10476,41 +10480,41 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +5.9% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>543361</v>
+        <v>2973</v>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>163</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>7898301056962</t>
+          <t>7898031313533</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>TERMÔMETRO DIGITAL G-TECH COM PONTA RIGIDA THGTH150V - VERDE</t>
+          <t>VASELINA SOLIDA 20G BISNAGA</t>
         </is>
       </c>
       <c r="E159" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G159" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H159" s="5" t="n">
-        <v>13.33</v>
+        <v>5.26</v>
       </c>
       <c r="I159" s="5">
         <f>G159*H159</f>
@@ -10521,13 +10525,13 @@
         <v/>
       </c>
       <c r="K159" s="5" t="n">
-        <v>12.59</v>
+        <v>5.26</v>
       </c>
       <c r="L159" s="5" t="n">
-        <v>12.59</v>
+        <v>5.06</v>
       </c>
       <c r="M159" s="5" t="n">
-        <v>12.59</v>
+        <v>5.126666666666666</v>
       </c>
       <c r="N159" s="6">
         <f>J159/M159-1</f>
@@ -10539,41 +10543,41 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +5.9% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>532641</v>
+        <v>591211</v>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>7898126050022</t>
+          <t>7898241250031</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>TESTE CONFIRME C/01 UND</t>
+          <t>VELA SEBO DE HOLANDA</t>
         </is>
       </c>
       <c r="E160" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G160" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H160" s="5" t="n">
-        <v>1.69</v>
+        <v>3.99</v>
       </c>
       <c r="I160" s="5">
         <f>G160*H160</f>
@@ -10584,13 +10588,13 @@
         <v/>
       </c>
       <c r="K160" s="5" t="n">
-        <v>1.69</v>
+        <v>0.4988</v>
       </c>
       <c r="L160" s="5" t="n">
-        <v>1.69</v>
+        <v>0.4988</v>
       </c>
       <c r="M160" s="5" t="n">
-        <v>1.69</v>
+        <v>0.4988</v>
       </c>
       <c r="N160" s="6">
         <f>J160/M160-1</f>
@@ -10602,41 +10606,45 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q160" s="2" t="inlineStr"/>
+          <t>OK (≤ últ. compra)</t>
+        </is>
+      </c>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>1 emb = 8 un</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>640411</v>
+        <v>4053</v>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>7368</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>7898126050220</t>
+          <t>7894164007127</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>TESTE GRAVIDEZ CONFIRME SEMANAS TIRA C/1</t>
+          <t>VITAXON C TRIPLA ACAO IMUNO C/30 CPR.</t>
         </is>
       </c>
       <c r="E161" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G161" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H161" s="5" t="n">
-        <v>7.71</v>
+        <v>14.84</v>
       </c>
       <c r="I161" s="5">
         <f>G161*H161</f>
@@ -10647,13 +10655,13 @@
         <v/>
       </c>
       <c r="K161" s="5" t="n">
-        <v>10.85</v>
+        <v>14.84</v>
       </c>
       <c r="L161" s="5" t="n">
-        <v>10.85</v>
+        <v>14.84</v>
       </c>
       <c r="M161" s="5" t="n">
-        <v>10.85</v>
+        <v>14.84</v>
       </c>
       <c r="N161" s="6">
         <f>J161/M161-1</f>
@@ -10665,41 +10673,41 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>461941</v>
+        <v>121961</v>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>6402</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>7893454100715</t>
+          <t>7896004774947</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>TIADOL 50MG/G POM DERM BG 20G</t>
+          <t>VOLIG 8MG CX 10 COMP</t>
         </is>
       </c>
       <c r="E162" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G162" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H162" s="5" t="n">
-        <v>13.89</v>
+        <v>7.31</v>
       </c>
       <c r="I162" s="5">
         <f>G162*H162</f>
@@ -10710,13 +10718,13 @@
         <v/>
       </c>
       <c r="K162" s="5" t="n">
-        <v>13.36</v>
+        <v>7.29</v>
       </c>
       <c r="L162" s="5" t="n">
-        <v>13.36</v>
+        <v>7.29</v>
       </c>
       <c r="M162" s="5" t="n">
-        <v>13.36</v>
+        <v>7.29</v>
       </c>
       <c r="N162" s="6">
         <f>J162/M162-1</f>
@@ -10728,664 +10736,26 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +4.0% (aceito, lim 5%)</t>
+          <t>REAJUSTE +0.3% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
-        <v>540941</v>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="C163" s="3" t="inlineStr">
-        <is>
-          <t>7898031310952</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t>TINTURA DE ARNICA 30ML</t>
-        </is>
-      </c>
-      <c r="E163" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F163" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="G163" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="H163" s="5" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="I163" s="5">
-        <f>G163*H163</f>
-        <v/>
-      </c>
-      <c r="J163" s="5">
-        <f>H163/E163</f>
-        <v/>
-      </c>
-      <c r="K163" s="5" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="L163" s="5" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="M163" s="5" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="N163" s="6">
-        <f>J163/M163-1</f>
-        <v/>
-      </c>
-      <c r="O163" s="6">
-        <f>J163/K163-1</f>
-        <v/>
-      </c>
-      <c r="P163" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q163" s="2" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="n">
-        <v>18001</v>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>1121</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="inlineStr">
-        <is>
-          <t>7896004739083</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t>TREXACONT 250MG 1BL X 12 COMP</t>
-        </is>
-      </c>
-      <c r="E164" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F164" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G164" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H164" s="5" t="n">
-        <v>35.81</v>
-      </c>
-      <c r="I164" s="5">
-        <f>G164*H164</f>
-        <v/>
-      </c>
-      <c r="J164" s="5">
-        <f>H164/E164</f>
-        <v/>
-      </c>
-      <c r="K164" s="5" t="n">
-        <v>40.53</v>
-      </c>
-      <c r="L164" s="5" t="n">
-        <v>40.53</v>
-      </c>
-      <c r="M164" s="5" t="n">
-        <v>40.53</v>
-      </c>
-      <c r="N164" s="6">
-        <f>J164/M164-1</f>
-        <v/>
-      </c>
-      <c r="O164" s="6">
-        <f>J164/K164-1</f>
-        <v/>
-      </c>
-      <c r="P164" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q164" s="2" t="inlineStr"/>
+      <c r="D163" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="I163" s="8">
+        <f>SUM(I2:I162)</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
-        <v>563961</v>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
-      </c>
-      <c r="C165" s="3" t="inlineStr">
-        <is>
-          <t>7898100243945</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
-        <is>
-          <t>TYFLEN 500MG CARTELA COM 10CP</t>
-        </is>
-      </c>
-      <c r="E165" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F165" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G165" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H165" s="5" t="n">
-        <v>29.55</v>
-      </c>
-      <c r="I165" s="5">
-        <f>G165*H165</f>
-        <v/>
-      </c>
-      <c r="J165" s="5">
-        <f>H165/E165</f>
-        <v/>
-      </c>
-      <c r="K165" s="5" t="n">
-        <v>1.8355</v>
-      </c>
-      <c r="L165" s="5" t="n">
-        <v>1.8355</v>
-      </c>
-      <c r="M165" s="5" t="n">
-        <v>1.8355</v>
-      </c>
-      <c r="N165" s="6">
-        <f>J165/M165-1</f>
-        <v/>
-      </c>
-      <c r="O165" s="6">
-        <f>J165/K165-1</f>
-        <v/>
-      </c>
-      <c r="P165" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q165" s="2" t="inlineStr">
-        <is>
-          <t>1 emb = 20 un</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="n">
-        <v>565801</v>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>3126</t>
-        </is>
-      </c>
-      <c r="C166" s="3" t="inlineStr">
-        <is>
-          <t>7898031310600</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>UNISSEPT ALCOOL GEL ANTISSEPTICO 450G</t>
-        </is>
-      </c>
-      <c r="E166" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F166" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="G166" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="H166" s="5" t="n">
-        <v>13.08</v>
-      </c>
-      <c r="I166" s="5">
-        <f>G166*H166</f>
-        <v/>
-      </c>
-      <c r="J166" s="5">
-        <f>H166/E166</f>
-        <v/>
-      </c>
-      <c r="K166" s="5" t="n">
-        <v>13.08</v>
-      </c>
-      <c r="L166" s="5" t="n">
-        <v>12.51</v>
-      </c>
-      <c r="M166" s="5" t="n">
-        <v>12.70333333333333</v>
-      </c>
-      <c r="N166" s="6">
-        <f>J166/M166-1</f>
-        <v/>
-      </c>
-      <c r="O166" s="6">
-        <f>J166/K166-1</f>
-        <v/>
-      </c>
-      <c r="P166" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
-        </is>
-      </c>
-      <c r="Q166" s="2" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="n">
-        <v>2973</v>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="C167" s="3" t="inlineStr">
-        <is>
-          <t>7898031313533</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
-        <is>
-          <t>VASELINA SOLIDA 20G BISNAGA</t>
-        </is>
-      </c>
-      <c r="E167" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F167" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="G167" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="H167" s="5" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="I167" s="5">
-        <f>G167*H167</f>
-        <v/>
-      </c>
-      <c r="J167" s="5">
-        <f>H167/E167</f>
-        <v/>
-      </c>
-      <c r="K167" s="5" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="L167" s="5" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="M167" s="5" t="n">
-        <v>5.126666666666666</v>
-      </c>
-      <c r="N167" s="6">
-        <f>J167/M167-1</f>
-        <v/>
-      </c>
-      <c r="O167" s="6">
-        <f>J167/K167-1</f>
-        <v/>
-      </c>
-      <c r="P167" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ últ. compra)</t>
-        </is>
-      </c>
-      <c r="Q167" s="2" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="n">
-        <v>604001</v>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="C168" s="3" t="inlineStr">
-        <is>
-          <t>7898031310495</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t>VASELINA SOLIDA 25G POTE (UNIPHAR)</t>
-        </is>
-      </c>
-      <c r="E168" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F168" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G168" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H168" s="5" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="I168" s="5">
-        <f>G168*H168</f>
-        <v/>
-      </c>
-      <c r="J168" s="5">
-        <f>H168/E168</f>
-        <v/>
-      </c>
-      <c r="K168" s="5" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="L168" s="5" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="M168" s="5" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="N168" s="6">
-        <f>J168/M168-1</f>
-        <v/>
-      </c>
-      <c r="O168" s="6">
-        <f>J168/K168-1</f>
-        <v/>
-      </c>
-      <c r="P168" s="2" t="inlineStr">
-        <is>
-          <t>REAJUSTE +6.7% (aceito, lim 10% zerado)</t>
-        </is>
-      </c>
-      <c r="Q168" s="2" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="n">
-        <v>591211</v>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>7292</t>
-        </is>
-      </c>
-      <c r="C169" s="3" t="inlineStr">
-        <is>
-          <t>7898241250031</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>VELA SEBO DE HOLANDA</t>
-        </is>
-      </c>
-      <c r="E169" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F169" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G169" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H169" s="5" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="I169" s="5">
-        <f>G169*H169</f>
-        <v/>
-      </c>
-      <c r="J169" s="5">
-        <f>H169/E169</f>
-        <v/>
-      </c>
-      <c r="K169" s="5" t="n">
-        <v>0.4988</v>
-      </c>
-      <c r="L169" s="5" t="n">
-        <v>0.4988</v>
-      </c>
-      <c r="M169" s="5" t="n">
-        <v>0.4988</v>
-      </c>
-      <c r="N169" s="6">
-        <f>J169/M169-1</f>
-        <v/>
-      </c>
-      <c r="O169" s="6">
-        <f>J169/K169-1</f>
-        <v/>
-      </c>
-      <c r="P169" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q169" s="2" t="inlineStr">
-        <is>
-          <t>1 emb = 8 un</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="n">
-        <v>4053</v>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>5175</t>
-        </is>
-      </c>
-      <c r="C170" s="3" t="inlineStr">
-        <is>
-          <t>7894164007127</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
-        <is>
-          <t>VITAXON C TRIPLA ACAO IMUNO C/30 CPR.</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F170" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G170" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H170" s="5" t="n">
-        <v>14.84</v>
-      </c>
-      <c r="I170" s="5">
-        <f>G170*H170</f>
-        <v/>
-      </c>
-      <c r="J170" s="5">
-        <f>H170/E170</f>
-        <v/>
-      </c>
-      <c r="K170" s="5" t="n">
-        <v>14.84</v>
-      </c>
-      <c r="L170" s="5" t="n">
-        <v>14.84</v>
-      </c>
-      <c r="M170" s="5" t="n">
-        <v>14.84</v>
-      </c>
-      <c r="N170" s="6">
-        <f>J170/M170-1</f>
-        <v/>
-      </c>
-      <c r="O170" s="6">
-        <f>J170/K170-1</f>
-        <v/>
-      </c>
-      <c r="P170" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q170" s="2" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="n">
-        <v>604081</v>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>5905</t>
-        </is>
-      </c>
-      <c r="C171" s="3" t="inlineStr">
-        <is>
-          <t>7894164007134</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>VITAXON C+ZINCO ACAO PROLONGADA 30CP</t>
-        </is>
-      </c>
-      <c r="E171" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F171" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G171" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H171" s="5" t="n">
-        <v>11.73</v>
-      </c>
-      <c r="I171" s="5">
-        <f>G171*H171</f>
-        <v/>
-      </c>
-      <c r="J171" s="5">
-        <f>H171/E171</f>
-        <v/>
-      </c>
-      <c r="K171" s="5" t="n">
-        <v>10.79</v>
-      </c>
-      <c r="L171" s="5" t="n">
-        <v>10.79</v>
-      </c>
-      <c r="M171" s="5" t="n">
-        <v>10.79</v>
-      </c>
-      <c r="N171" s="6">
-        <f>J171/M171-1</f>
-        <v/>
-      </c>
-      <c r="O171" s="6">
-        <f>J171/K171-1</f>
-        <v/>
-      </c>
-      <c r="P171" s="2" t="inlineStr">
-        <is>
-          <t>REAJUSTE +8.7% (aceito, lim 10% zerado)</t>
-        </is>
-      </c>
-      <c r="Q171" s="2" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="n">
-        <v>121961</v>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>6402</t>
-        </is>
-      </c>
-      <c r="C172" s="3" t="inlineStr">
-        <is>
-          <t>7896004774947</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
-        <is>
-          <t>VOLIG 8MG CX 10 COMP</t>
-        </is>
-      </c>
-      <c r="E172" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F172" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G172" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H172" s="5" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="I172" s="5">
-        <f>G172*H172</f>
-        <v/>
-      </c>
-      <c r="J172" s="5">
-        <f>H172/E172</f>
-        <v/>
-      </c>
-      <c r="K172" s="5" t="n">
-        <v>7.29</v>
-      </c>
-      <c r="L172" s="5" t="n">
-        <v>7.29</v>
-      </c>
-      <c r="M172" s="5" t="n">
-        <v>7.29</v>
-      </c>
-      <c r="N172" s="6">
-        <f>J172/M172-1</f>
-        <v/>
-      </c>
-      <c r="O172" s="6">
-        <f>J172/K172-1</f>
-        <v/>
-      </c>
-      <c r="P172" s="2" t="inlineStr">
-        <is>
-          <t>REAJUSTE +0.3% (aceito, lim 5%)</t>
-        </is>
-      </c>
-      <c r="Q172" s="2" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="D173" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="I173" s="8">
-        <f>SUM(I2:I172)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="9" t="inlineStr">
-        <is>
-          <t>Pedido FINAL DIMEC — cotação 08/09/2026 (fechada 09/09). Somente itens aprovados: preço até 5% acima da referência (últ. compra; sem ela, menor histórico), 10% quando o item está zerado. 'Qtd pedido' na embalagem do fornecedor.</t>
+      <c r="A165" s="9" t="inlineStr">
+        <is>
+          <t>Pedido FINAL DIMEC — cotação 08/09/2026 (fechada 09/09). Somente itens aprovados: teto de reajuste de 4% sobre a última compra OU 6% sobre a média histórica (3/6/12m). 'Qtd pedido' na embalagem do fornecedor.</t>
         </is>
       </c>
     </row>
